--- a/Execution/excel_files/analytics_dw.public.dim_vehicle_master.xlsx
+++ b/Execution/excel_files/analytics_dw.public.dim_vehicle_master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\ETL_Testing_Databricks_Multi_Source\Execution\excel_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\ETL_Testing_Databricks_Multi_Source\ETL_Testing_Multi\Execution\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE7E1E1-1D4A-4FEB-9A9C-0722141D266A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E377BA96-B0F4-49CD-9A40-7E16CEE45E31}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6936" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -607,7 +607,7 @@
     <t>analytics_dw.public.dim_vehicle_master.xlsx</t>
   </si>
   <si>
-    <t>xl_m</t>
+    <t>xl</t>
   </si>
 </sst>
 </file>
